--- a/printing/regression/model_report0901_03.xlsx
+++ b/printing/regression/model_report0901_03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cchih\Desktop\NTHU\MasterThesis\GA\SGM_GA\printing\regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B957BB-5260-4814-BA89-2F29285AD96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E957914C-72E7-4727-B17A-C11806D772D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/printing/regression/model_report0901_03.xlsx
+++ b/printing/regression/model_report0901_03.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cchih\Desktop\NTHU\MasterThesis\GA\SGM_GA\printing\regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E957914C-72E7-4727-B17A-C11806D772D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328D0163-69E1-4B0F-9005-2D35356079C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="overall_train" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,20 @@
     <sheet name="ang_model_coeffs" sheetId="6" r:id="rId6"/>
     <sheet name="run_parameters" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1445,6 +1458,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="78.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
